--- a/research/LBTYA/Reports/LBTYA_DCF_Model.xlsx
+++ b/research/LBTYA/Reports/LBTYA_DCF_Model.xlsx
@@ -2227,9 +2227,10 @@
       </c>
     </row>
     <row r="11" spans="1:4">
-      <c r="A11">
-        <f> Consolidated FCF ex-JV distributions</f>
-        <v>0</v>
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>= Consolidated FCF ex-JV distributions</t>
+        </is>
       </c>
       <c r="B11" s="7">
         <v>-260.4</v>
